--- a/research/traditional_assets/database/data/netherlands/netherlands_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_financial_svcs_non_bank_insurance.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.185</v>
+        <v>0.204</v>
       </c>
       <c r="E2">
-        <v>0.149</v>
+        <v>0.179</v>
       </c>
       <c r="F2">
-        <v>0.0781</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="G2">
-        <v>0.41923474663909</v>
+        <v>0.5131874478598473</v>
       </c>
       <c r="H2">
-        <v>0.4087556015167184</v>
+        <v>0.5025989860745684</v>
       </c>
       <c r="I2">
-        <v>0.4564632885211996</v>
+        <v>0.4200089841493936</v>
       </c>
       <c r="J2">
-        <v>0.2760396960315303</v>
+        <v>0.2609203845142206</v>
       </c>
       <c r="K2">
-        <v>429.93</v>
+        <v>461.8</v>
       </c>
       <c r="L2">
-        <v>0.2964012409513961</v>
+        <v>0.2963485849964705</v>
       </c>
       <c r="M2">
-        <v>187.58</v>
+        <v>238.2</v>
       </c>
       <c r="N2">
-        <v>0.01669960650250165</v>
+        <v>0.02981301158977696</v>
       </c>
       <c r="O2">
-        <v>0.4363035843044216</v>
+        <v>0.5158077089649198</v>
       </c>
       <c r="P2">
-        <v>182.2</v>
+        <v>202</v>
       </c>
       <c r="Q2">
-        <v>0.01622064348414436</v>
+        <v>0.02528223484943303</v>
       </c>
       <c r="R2">
-        <v>0.4237899192891866</v>
+        <v>0.4374187960155911</v>
       </c>
       <c r="S2">
-        <v>5.379999999999995</v>
+        <v>36.19999999999999</v>
       </c>
       <c r="T2">
-        <v>0.02868109606567862</v>
+        <v>0.1519731318219983</v>
       </c>
       <c r="U2">
-        <v>1015.5</v>
+        <v>1278.4</v>
       </c>
       <c r="V2">
-        <v>0.09040649537952032</v>
+        <v>0.1600040051065108</v>
       </c>
       <c r="W2">
-        <v>0.2058160865069116</v>
+        <v>0.1465531673748552</v>
       </c>
       <c r="X2">
-        <v>0.02929300578667805</v>
+        <v>0.05896641926798755</v>
       </c>
       <c r="Y2">
-        <v>0.1765230807202335</v>
+        <v>0.08758674810686762</v>
       </c>
       <c r="Z2">
-        <v>0.6143148705703578</v>
+        <v>0.2139737505576595</v>
       </c>
       <c r="AA2">
-        <v>0.1155517952837423</v>
+        <v>0.0350850146840493</v>
       </c>
       <c r="AB2">
-        <v>0.02572278429266969</v>
+        <v>0.04832508303454214</v>
       </c>
       <c r="AC2">
-        <v>0.08982901099107263</v>
+        <v>-0.01324006835049284</v>
       </c>
       <c r="AD2">
-        <v>4072.3</v>
+        <v>3336.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4072.3</v>
+        <v>3336.5</v>
       </c>
       <c r="AG2">
-        <v>3056.8</v>
+        <v>2058.1</v>
       </c>
       <c r="AH2">
-        <v>0.266078184110971</v>
+        <v>0.2945798716262151</v>
       </c>
       <c r="AI2">
-        <v>0.4851210330696654</v>
+        <v>0.461059060884946</v>
       </c>
       <c r="AJ2">
-        <v>0.2139208084314247</v>
+        <v>0.2048288697140696</v>
       </c>
       <c r="AK2">
-        <v>0.4142622884169727</v>
+        <v>0.3454231143633983</v>
       </c>
       <c r="AL2">
-        <v>42.5</v>
+        <v>43.3</v>
       </c>
       <c r="AM2">
-        <v>35.03</v>
+        <v>37.19</v>
       </c>
       <c r="AN2">
-        <v>5.703501400560224</v>
+        <v>4.492997576084029</v>
       </c>
       <c r="AO2">
-        <v>15.57882352941177</v>
+        <v>15.11547344110855</v>
       </c>
       <c r="AP2">
-        <v>4.281232492997199</v>
+        <v>2.771478588742257</v>
       </c>
       <c r="AQ2">
-        <v>18.90094204967171</v>
+        <v>17.59881688625975</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.185</v>
+        <v>0.204</v>
       </c>
       <c r="E3">
-        <v>0.149</v>
+        <v>0.179</v>
       </c>
       <c r="F3">
-        <v>0.0781</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="G3">
-        <v>0.4520853468143633</v>
+        <v>0.5656787154276014</v>
       </c>
       <c r="H3">
-        <v>0.4407850717418779</v>
+        <v>0.5540072151092877</v>
       </c>
       <c r="I3">
-        <v>0.4922310608876664</v>
+        <v>0.4629695126264413</v>
       </c>
       <c r="J3">
-        <v>0.3492239671306738</v>
+        <v>0.343732383374846</v>
       </c>
       <c r="K3">
-        <v>426.3</v>
+        <v>442.5</v>
       </c>
       <c r="L3">
-        <v>0.3169281094342428</v>
+        <v>0.3130084176275023</v>
       </c>
       <c r="M3">
-        <v>187.58</v>
+        <v>238.2</v>
       </c>
       <c r="N3">
-        <v>0.01698478812024629</v>
+        <v>0.03023725198979398</v>
       </c>
       <c r="O3">
-        <v>0.4400187661271405</v>
+        <v>0.5383050847457627</v>
       </c>
       <c r="P3">
-        <v>182.2</v>
+        <v>202</v>
       </c>
       <c r="Q3">
-        <v>0.0164976457805143</v>
+        <v>0.02564200210721404</v>
       </c>
       <c r="R3">
-        <v>0.4273985456251466</v>
+        <v>0.4564971751412429</v>
       </c>
       <c r="S3">
-        <v>5.379999999999995</v>
+        <v>36.19999999999999</v>
       </c>
       <c r="T3">
-        <v>0.02868109606567862</v>
+        <v>0.1519731318219983</v>
       </c>
       <c r="U3">
-        <v>925.2</v>
+        <v>1189.4</v>
       </c>
       <c r="V3">
-        <v>0.08377399492937342</v>
+        <v>0.1509831549817841</v>
       </c>
       <c r="W3">
-        <v>0.3757271285034374</v>
+        <v>0.1073508005822416</v>
       </c>
       <c r="X3">
-        <v>0.02492365102449957</v>
+        <v>0.05079810019285823</v>
       </c>
       <c r="Y3">
-        <v>0.3508034774789378</v>
+        <v>0.0565527003893834</v>
       </c>
       <c r="Z3">
-        <v>0.6617632588802518</v>
+        <v>0.2041414564410622</v>
       </c>
       <c r="AA3">
-        <v>0.2311035905674846</v>
+        <v>0.0701700293680986</v>
       </c>
       <c r="AB3">
-        <v>0.02450326484032401</v>
+        <v>0.04880727005320393</v>
       </c>
       <c r="AC3">
-        <v>0.2066003257271606</v>
+        <v>0.02136275931489467</v>
       </c>
       <c r="AD3">
-        <v>3728.3</v>
+        <v>3029</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3728.3</v>
+        <v>3029</v>
       </c>
       <c r="AG3">
-        <v>2803.1</v>
+        <v>1839.6</v>
       </c>
       <c r="AH3">
-        <v>0.2523845305064208</v>
+        <v>0.277719200124694</v>
       </c>
       <c r="AI3">
-        <v>0.4692400634329297</v>
+        <v>0.4435755498930967</v>
       </c>
       <c r="AJ3">
-        <v>0.2024322782387648</v>
+        <v>0.1893118458831157</v>
       </c>
       <c r="AK3">
-        <v>0.3992906185008974</v>
+        <v>0.3262164846077458</v>
       </c>
       <c r="AL3">
-        <v>42.5</v>
+        <v>43.3</v>
       </c>
       <c r="AM3">
-        <v>35.03</v>
+        <v>37.19</v>
       </c>
       <c r="AN3">
-        <v>5.221708683473389</v>
+        <v>4.078911931053057</v>
       </c>
       <c r="AO3">
-        <v>15.57882352941177</v>
+        <v>15.11547344110855</v>
       </c>
       <c r="AP3">
-        <v>3.925910364145659</v>
+        <v>2.477242122273094</v>
       </c>
       <c r="AQ3">
-        <v>18.90094204967171</v>
+        <v>17.59881688625975</v>
       </c>
     </row>
     <row r="4">
@@ -874,10 +874,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3.63</v>
+        <v>19.3</v>
       </c>
       <c r="L4">
-        <v>0.03444022770398482</v>
+        <v>0.1334716459197787</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -901,55 +901,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>90.3</v>
+        <v>89</v>
       </c>
       <c r="V4">
-        <v>0.4787910922587487</v>
+        <v>0.7939339875111509</v>
       </c>
       <c r="W4">
-        <v>0.03590504451038576</v>
+        <v>0.1857555341674687</v>
       </c>
       <c r="X4">
-        <v>0.03366236054885654</v>
+        <v>0.06713473834311687</v>
       </c>
       <c r="Y4">
-        <v>0.00224268396152922</v>
+        <v>0.1186207958243518</v>
       </c>
       <c r="Z4">
-        <v>0.32078693234561</v>
+        <v>0.4043974729352937</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.02694230374501538</v>
+        <v>0.04784289601588036</v>
       </c>
       <c r="AC4">
-        <v>-0.02694230374501538</v>
+        <v>-0.04784289601588036</v>
       </c>
       <c r="AD4">
-        <v>344</v>
+        <v>307.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>344</v>
+        <v>307.5</v>
       </c>
       <c r="AG4">
-        <v>253.7</v>
+        <v>218.5</v>
       </c>
       <c r="AH4">
-        <v>0.6458880961321817</v>
+        <v>0.732840800762631</v>
       </c>
       <c r="AI4">
-        <v>0.7661469933184856</v>
+        <v>0.7536764705882353</v>
       </c>
       <c r="AJ4">
-        <v>0.5735925842188561</v>
+        <v>0.660919540229885</v>
       </c>
       <c r="AK4">
-        <v>0.7072762754390856</v>
+        <v>0.6849529780564263</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.204</v>
+        <v>0.194</v>
       </c>
       <c r="E2">
-        <v>0.179</v>
+        <v>0.122</v>
       </c>
       <c r="F2">
-        <v>0.04679999999999999</v>
+        <v>0.1399</v>
       </c>
       <c r="G2">
-        <v>0.5131874478598473</v>
+        <v>0.1964702667792737</v>
       </c>
       <c r="H2">
-        <v>0.5025989860745684</v>
+        <v>0.190247901038303</v>
       </c>
       <c r="I2">
-        <v>0.4200089841493936</v>
+        <v>0.1726240747180685</v>
       </c>
       <c r="J2">
-        <v>0.2609203845142206</v>
+        <v>0.116595022079233</v>
       </c>
       <c r="K2">
-        <v>461.8</v>
+        <v>1134.95</v>
       </c>
       <c r="L2">
-        <v>0.2963485849964705</v>
+        <v>0.1409595608326296</v>
       </c>
       <c r="M2">
-        <v>238.2</v>
+        <v>336.9</v>
       </c>
       <c r="N2">
-        <v>0.02981301158977696</v>
+        <v>0.006829847793121902</v>
       </c>
       <c r="O2">
-        <v>0.5158077089649198</v>
+        <v>0.2968412705405524</v>
       </c>
       <c r="P2">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="Q2">
-        <v>0.02528223484943303</v>
+        <v>0.00508842919582546</v>
       </c>
       <c r="R2">
-        <v>0.4374187960155911</v>
+        <v>0.2211551169655051</v>
       </c>
       <c r="S2">
-        <v>36.19999999999999</v>
+        <v>85.89999999999998</v>
       </c>
       <c r="T2">
-        <v>0.1519731318219983</v>
+        <v>0.2549718017215791</v>
       </c>
       <c r="U2">
-        <v>1278.4</v>
+        <v>8481</v>
       </c>
       <c r="V2">
-        <v>0.1600040051065108</v>
+        <v>0.1719321434653216</v>
       </c>
       <c r="W2">
-        <v>0.1465531673748552</v>
+        <v>0.1373704750370071</v>
       </c>
       <c r="X2">
-        <v>0.05896641926798755</v>
+        <v>0.05271887344160027</v>
       </c>
       <c r="Y2">
-        <v>0.08758674810686762</v>
+        <v>0.08465160159540687</v>
       </c>
       <c r="Z2">
-        <v>0.2139737505576595</v>
+        <v>1.370648417683809</v>
       </c>
       <c r="AA2">
-        <v>0.0350850146840493</v>
+        <v>0.09715929830533447</v>
       </c>
       <c r="AB2">
-        <v>0.04832508303454214</v>
+        <v>0.04905266530744195</v>
       </c>
       <c r="AC2">
-        <v>-0.01324006835049284</v>
+        <v>0.04810663299789252</v>
       </c>
       <c r="AD2">
-        <v>3336.5</v>
+        <v>3762.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3336.5</v>
+        <v>3762.7</v>
       </c>
       <c r="AG2">
-        <v>2058.1</v>
+        <v>-4718.299999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2945798716262151</v>
+        <v>0.07087358707711201</v>
       </c>
       <c r="AI2">
-        <v>0.461059060884946</v>
+        <v>0.3376011628115635</v>
       </c>
       <c r="AJ2">
-        <v>0.2048288697140696</v>
+        <v>-0.1057694247612045</v>
       </c>
       <c r="AK2">
-        <v>0.3454231143633983</v>
+        <v>-1.77086773757694</v>
       </c>
       <c r="AL2">
-        <v>43.3</v>
+        <v>39.68000000000001</v>
       </c>
       <c r="AM2">
-        <v>37.19</v>
+        <v>-110.32</v>
       </c>
       <c r="AN2">
-        <v>4.492997576084029</v>
+        <v>2.468963254593176</v>
       </c>
       <c r="AO2">
-        <v>15.11547344110855</v>
+        <v>35.02772177419354</v>
       </c>
       <c r="AP2">
-        <v>2.771478588742257</v>
+        <v>-3.095997375328083</v>
       </c>
       <c r="AQ2">
-        <v>17.59881688625975</v>
+        <v>-12.59880348078318</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Euronext N.V. (ENXTPA:ENX)</t>
+          <t>Adyen N.V. (ENXTAM:ADYEN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.204</v>
+        <v>0.358</v>
       </c>
       <c r="E3">
-        <v>0.179</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="F3">
-        <v>0.04679999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="G3">
-        <v>0.5656787154276014</v>
+        <v>0.117038291466742</v>
       </c>
       <c r="H3">
-        <v>0.5540072151092877</v>
+        <v>0.116144510302004</v>
       </c>
       <c r="I3">
-        <v>0.4629695126264413</v>
+        <v>0.106140433405463</v>
       </c>
       <c r="J3">
-        <v>0.343732383374846</v>
+        <v>0.08165362594856944</v>
       </c>
       <c r="K3">
-        <v>442.5</v>
+        <v>615.9</v>
       </c>
       <c r="L3">
-        <v>0.3130084176275023</v>
+        <v>0.09657540690563553</v>
       </c>
       <c r="M3">
-        <v>238.2</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03023725198979398</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.5383050847457627</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>202</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02564200210721404</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.4564971751412429</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>36.19999999999999</v>
-      </c>
-      <c r="T3">
-        <v>0.1519731318219983</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1189.4</v>
+        <v>6999.6</v>
       </c>
       <c r="V3">
-        <v>0.1509831549817841</v>
+        <v>0.1749904374760937</v>
       </c>
       <c r="W3">
-        <v>0.1073508005822416</v>
+        <v>0.2805028009290887</v>
       </c>
       <c r="X3">
-        <v>0.05079810019285823</v>
+        <v>0.04986335738423112</v>
       </c>
       <c r="Y3">
-        <v>0.0565527003893834</v>
-      </c>
-      <c r="Z3">
-        <v>0.2041414564410622</v>
-      </c>
-      <c r="AA3">
-        <v>0.0701700293680986</v>
+        <v>0.2306394435448576</v>
       </c>
       <c r="AB3">
-        <v>0.04880727005320393</v>
-      </c>
-      <c r="AC3">
-        <v>0.02136275931489467</v>
+        <v>0.04979518369051127</v>
       </c>
       <c r="AD3">
-        <v>3029</v>
+        <v>226.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3029</v>
+        <v>226.1</v>
       </c>
       <c r="AG3">
-        <v>1839.6</v>
+        <v>-6773.5</v>
       </c>
       <c r="AH3">
-        <v>0.277719200124694</v>
+        <v>0.005620742803162134</v>
       </c>
       <c r="AI3">
-        <v>0.4435755498930967</v>
+        <v>0.07041639415740135</v>
       </c>
       <c r="AJ3">
-        <v>0.1893118458831157</v>
+        <v>-0.2038589796065779</v>
       </c>
       <c r="AK3">
-        <v>0.3262164846077458</v>
+        <v>1.787816401404176</v>
       </c>
       <c r="AL3">
-        <v>43.3</v>
+        <v>5.98</v>
       </c>
       <c r="AM3">
-        <v>37.19</v>
+        <v>-126.42</v>
       </c>
       <c r="AN3">
-        <v>4.078911931053057</v>
+        <v>0.314508276533593</v>
       </c>
       <c r="AO3">
-        <v>15.11547344110855</v>
+        <v>113.1939799331104</v>
       </c>
       <c r="AP3">
-        <v>2.477242122273094</v>
+        <v>-9.422033662539992</v>
       </c>
       <c r="AQ3">
-        <v>17.59881688625975</v>
+        <v>-5.354374307862679</v>
       </c>
     </row>
     <row r="4">
@@ -853,108 +841,251 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Euronext N.V. (ENXTPA:ENX)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.194</v>
+      </c>
+      <c r="E4">
+        <v>0.122</v>
+      </c>
+      <c r="F4">
+        <v>0.0678</v>
+      </c>
+      <c r="G4">
+        <v>0.5452587613391634</v>
+      </c>
+      <c r="H4">
+        <v>0.5162827122626118</v>
+      </c>
+      <c r="I4">
+        <v>0.4653135808914703</v>
+      </c>
+      <c r="J4">
+        <v>0.3522349526959235</v>
+      </c>
+      <c r="K4">
+        <v>510.4</v>
+      </c>
+      <c r="L4">
+        <v>0.3330940416367552</v>
+      </c>
+      <c r="M4">
+        <v>336.9</v>
+      </c>
+      <c r="N4">
+        <v>0.03642280290171573</v>
+      </c>
+      <c r="O4">
+        <v>0.6600705329153604</v>
+      </c>
+      <c r="P4">
+        <v>251</v>
+      </c>
+      <c r="Q4">
+        <v>0.02713601522211531</v>
+      </c>
+      <c r="R4">
+        <v>0.4917711598746082</v>
+      </c>
+      <c r="S4">
+        <v>85.89999999999998</v>
+      </c>
+      <c r="T4">
+        <v>0.2549718017215791</v>
+      </c>
+      <c r="U4">
+        <v>1414.6</v>
+      </c>
+      <c r="V4">
+        <v>0.1529346897737224</v>
+      </c>
+      <c r="W4">
+        <v>0.1373704750370071</v>
+      </c>
+      <c r="X4">
+        <v>0.05271887344160027</v>
+      </c>
+      <c r="Y4">
+        <v>0.08465160159540687</v>
+      </c>
+      <c r="Z4">
+        <v>0.2758366186027254</v>
+      </c>
+      <c r="AA4">
+        <v>0.09715929830533447</v>
+      </c>
+      <c r="AB4">
+        <v>0.04905266530744195</v>
+      </c>
+      <c r="AC4">
+        <v>0.04810663299789252</v>
+      </c>
+      <c r="AD4">
+        <v>3283.3</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>3283.3</v>
+      </c>
+      <c r="AG4">
+        <v>1868.7</v>
+      </c>
+      <c r="AH4">
+        <v>0.2619723928827895</v>
+      </c>
+      <c r="AI4">
+        <v>0.4313321071991593</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1680727442797525</v>
+      </c>
+      <c r="AK4">
+        <v>0.3015296737341466</v>
+      </c>
+      <c r="AL4">
+        <v>33.7</v>
+      </c>
+      <c r="AM4">
+        <v>16.1</v>
+      </c>
+      <c r="AN4">
+        <v>4.078126940752702</v>
+      </c>
+      <c r="AO4">
+        <v>21.15727002967359</v>
+      </c>
+      <c r="AP4">
+        <v>2.321078126940753</v>
+      </c>
+      <c r="AQ4">
+        <v>44.28571428571428</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>ASA International Group PLC (LSE:ASAI)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>19.3</v>
-      </c>
-      <c r="L4">
-        <v>0.1334716459197787</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>89</v>
-      </c>
-      <c r="V4">
-        <v>0.7939339875111509</v>
-      </c>
-      <c r="W4">
-        <v>0.1857555341674687</v>
-      </c>
-      <c r="X4">
-        <v>0.06713473834311687</v>
-      </c>
-      <c r="Y4">
-        <v>0.1186207958243518</v>
-      </c>
-      <c r="Z4">
-        <v>0.4043974729352937</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.04784289601588036</v>
-      </c>
-      <c r="AC4">
-        <v>-0.04784289601588036</v>
-      </c>
-      <c r="AD4">
-        <v>307.5</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>307.5</v>
-      </c>
-      <c r="AG4">
-        <v>218.5</v>
-      </c>
-      <c r="AH4">
-        <v>0.732840800762631</v>
-      </c>
-      <c r="AI4">
-        <v>0.7536764705882353</v>
-      </c>
-      <c r="AJ4">
-        <v>0.660919540229885</v>
-      </c>
-      <c r="AK4">
-        <v>0.6849529780564263</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="D5">
+        <v>0.06179999999999999</v>
+      </c>
+      <c r="E5">
+        <v>-0.189</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>8.65</v>
+      </c>
+      <c r="L5">
+        <v>0.0609584214235377</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>66.8</v>
+      </c>
+      <c r="V5">
+        <v>0.8564102564102564</v>
+      </c>
+      <c r="W5">
+        <v>0.08589870903674281</v>
+      </c>
+      <c r="X5">
+        <v>0.07636404514803898</v>
+      </c>
+      <c r="Y5">
+        <v>0.009534663888703832</v>
+      </c>
+      <c r="Z5">
+        <v>0.4445488721804511</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.04682922298384256</v>
+      </c>
+      <c r="AC5">
+        <v>-0.04682922298384256</v>
+      </c>
+      <c r="AD5">
+        <v>253.3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>253.3</v>
+      </c>
+      <c r="AG5">
+        <v>186.5</v>
+      </c>
+      <c r="AH5">
+        <v>0.7645638394204648</v>
+      </c>
+      <c r="AI5">
+        <v>0.7854263565891473</v>
+      </c>
+      <c r="AJ5">
+        <v>0.7051039697542533</v>
+      </c>
+      <c r="AK5">
+        <v>0.7293703558858037</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/netherlands/netherlands_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.194</v>
+        <v>0.2695</v>
       </c>
       <c r="E2">
-        <v>0.122</v>
+        <v>0.2855</v>
       </c>
       <c r="F2">
-        <v>0.1399</v>
+        <v>0.1732</v>
       </c>
       <c r="G2">
-        <v>0.1964702667792737</v>
+        <v>0.4720156397465282</v>
       </c>
       <c r="H2">
-        <v>0.190247901038303</v>
+        <v>0.4521504651476338</v>
       </c>
       <c r="I2">
-        <v>0.1726240747180685</v>
+        <v>0.4676014561143319</v>
       </c>
       <c r="J2">
-        <v>0.116595022079233</v>
+        <v>0.3488216757487996</v>
       </c>
       <c r="K2">
-        <v>1134.95</v>
+        <v>1522.3</v>
       </c>
       <c r="L2">
-        <v>0.1409595608326296</v>
+        <v>0.4104894162060132</v>
       </c>
       <c r="M2">
-        <v>336.9</v>
+        <v>456.3</v>
       </c>
       <c r="N2">
-        <v>0.006829847793121902</v>
+        <v>0.007806124805616714</v>
       </c>
       <c r="O2">
-        <v>0.2968412705405524</v>
+        <v>0.2997438087105038</v>
       </c>
       <c r="P2">
-        <v>251</v>
+        <v>286.9</v>
       </c>
       <c r="Q2">
-        <v>0.00508842919582546</v>
+        <v>0.004908124494261309</v>
       </c>
       <c r="R2">
-        <v>0.2211551169655051</v>
+        <v>0.1884648229652499</v>
       </c>
       <c r="S2">
-        <v>85.89999999999998</v>
+        <v>169.4</v>
       </c>
       <c r="T2">
-        <v>0.2549718017215791</v>
+        <v>0.371246986631602</v>
       </c>
       <c r="U2">
-        <v>8481</v>
+        <v>11177.9</v>
       </c>
       <c r="V2">
-        <v>0.1719321434653216</v>
+        <v>0.1912252519498205</v>
       </c>
       <c r="W2">
-        <v>0.1373704750370071</v>
+        <v>0.2243606774443286</v>
       </c>
       <c r="X2">
-        <v>0.05271887344160027</v>
+        <v>0.05734270109563393</v>
       </c>
       <c r="Y2">
-        <v>0.08465160159540687</v>
+        <v>0.1670179763486946</v>
       </c>
       <c r="Z2">
-        <v>1.370648417683809</v>
-      </c>
-      <c r="AA2">
-        <v>0.09715929830533447</v>
+        <v>0.6124791491188954</v>
       </c>
       <c r="AB2">
-        <v>0.04905266530744195</v>
-      </c>
-      <c r="AC2">
-        <v>0.04810663299789252</v>
+        <v>0.05539773458889831</v>
       </c>
       <c r="AD2">
-        <v>3762.7</v>
+        <v>3705.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3762.7</v>
+        <v>3705.5</v>
       </c>
       <c r="AG2">
-        <v>-4718.299999999999</v>
+        <v>-7472.4</v>
       </c>
       <c r="AH2">
-        <v>0.07087358707711201</v>
+        <v>0.05961267447023469</v>
       </c>
       <c r="AI2">
-        <v>0.3376011628115635</v>
+        <v>0.3018245499714914</v>
       </c>
       <c r="AJ2">
-        <v>-0.1057694247612045</v>
+        <v>-0.1465702399096146</v>
       </c>
       <c r="AK2">
-        <v>-1.77086773757694</v>
+        <v>-6.798653443726683</v>
       </c>
       <c r="AL2">
-        <v>39.68000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="AM2">
-        <v>-110.32</v>
+        <v>-345.9</v>
       </c>
       <c r="AN2">
-        <v>2.468963254593176</v>
+        <v>2.014296586214395</v>
       </c>
       <c r="AO2">
-        <v>35.02772177419354</v>
+        <v>30.15826086956521</v>
       </c>
       <c r="AP2">
-        <v>-3.095997375328083</v>
+        <v>-4.061969993476843</v>
       </c>
       <c r="AQ2">
-        <v>-12.59880348078318</v>
+        <v>-5.013298641225788</v>
       </c>
     </row>
     <row r="3">
@@ -725,31 +719,31 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.358</v>
+        <v>0.344</v>
       </c>
       <c r="E3">
-        <v>0.4379999999999999</v>
+        <v>0.363</v>
       </c>
       <c r="F3">
-        <v>0.212</v>
+        <v>0.268</v>
       </c>
       <c r="G3">
-        <v>0.117038291466742</v>
+        <v>0.4165481344052772</v>
       </c>
       <c r="H3">
-        <v>0.116144510302004</v>
+        <v>0.4146052360338074</v>
       </c>
       <c r="I3">
-        <v>0.106140433405463</v>
+        <v>0.4314574314574315</v>
       </c>
       <c r="J3">
-        <v>0.08165362594856944</v>
+        <v>0.3206396231761593</v>
       </c>
       <c r="K3">
-        <v>615.9</v>
+        <v>884.8</v>
       </c>
       <c r="L3">
-        <v>0.09657540690563553</v>
+        <v>0.4559884559884559</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -773,64 +767,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6999.6</v>
+        <v>9359.6</v>
       </c>
       <c r="V3">
-        <v>0.1749904374760937</v>
+        <v>0.1998603480195684</v>
       </c>
       <c r="W3">
-        <v>0.2805028009290887</v>
+        <v>0.2964352720450281</v>
       </c>
       <c r="X3">
-        <v>0.04986335738423112</v>
+        <v>0.05621797122880066</v>
       </c>
       <c r="Y3">
-        <v>0.2306394435448576</v>
+        <v>0.2402173008162275</v>
       </c>
       <c r="AB3">
-        <v>0.04979518369051127</v>
+        <v>0.05613791393903839</v>
       </c>
       <c r="AD3">
-        <v>226.1</v>
+        <v>248.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>226.1</v>
+        <v>248.2</v>
       </c>
       <c r="AG3">
-        <v>-6773.5</v>
+        <v>-9111.4</v>
       </c>
       <c r="AH3">
-        <v>0.005620742803162134</v>
+        <v>0.005272000832644773</v>
       </c>
       <c r="AI3">
-        <v>0.07041639415740135</v>
+        <v>0.06084078931241573</v>
       </c>
       <c r="AJ3">
-        <v>-0.2038589796065779</v>
+        <v>-0.2415580352763705</v>
       </c>
       <c r="AK3">
-        <v>1.787816401404176</v>
+        <v>1.72561125736255</v>
       </c>
       <c r="AL3">
-        <v>5.98</v>
+        <v>17.5</v>
       </c>
       <c r="AM3">
-        <v>-126.42</v>
+        <v>-335.9</v>
       </c>
       <c r="AN3">
-        <v>0.314508276533593</v>
+        <v>0.2788450735872374</v>
       </c>
       <c r="AO3">
-        <v>113.1939799331104</v>
+        <v>47.84</v>
       </c>
       <c r="AP3">
-        <v>-9.422033662539992</v>
+        <v>-10.23637793506347</v>
       </c>
       <c r="AQ3">
-        <v>-5.354374307862679</v>
+        <v>-2.492408454897291</v>
       </c>
     </row>
     <row r="4">
@@ -850,243 +844,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.194</v>
+        <v>0.195</v>
       </c>
       <c r="E4">
-        <v>0.122</v>
+        <v>0.208</v>
       </c>
       <c r="F4">
-        <v>0.0678</v>
+        <v>0.0784</v>
       </c>
       <c r="G4">
-        <v>0.5452587613391634</v>
+        <v>0.5328884112889543</v>
       </c>
       <c r="H4">
-        <v>0.5162827122626118</v>
+        <v>0.4933544482778123</v>
       </c>
       <c r="I4">
-        <v>0.4653135808914703</v>
+        <v>0.5072676884791585</v>
       </c>
       <c r="J4">
-        <v>0.3522349526959235</v>
+        <v>0.3798454685847933</v>
       </c>
       <c r="K4">
-        <v>510.4</v>
+        <v>637.5</v>
       </c>
       <c r="L4">
-        <v>0.3330940416367552</v>
+        <v>0.3605565296080538</v>
       </c>
       <c r="M4">
-        <v>336.9</v>
+        <v>456.3</v>
       </c>
       <c r="N4">
-        <v>0.03642280290171573</v>
+        <v>0.03925701601940912</v>
       </c>
       <c r="O4">
-        <v>0.6600705329153604</v>
+        <v>0.7157647058823529</v>
       </c>
       <c r="P4">
-        <v>251</v>
+        <v>286.9</v>
       </c>
       <c r="Q4">
-        <v>0.02713601522211531</v>
+        <v>0.02468296711805496</v>
       </c>
       <c r="R4">
-        <v>0.4917711598746082</v>
+        <v>0.4500392156862745</v>
       </c>
       <c r="S4">
-        <v>85.89999999999998</v>
+        <v>169.4</v>
       </c>
       <c r="T4">
-        <v>0.2549718017215791</v>
+        <v>0.371246986631602</v>
       </c>
       <c r="U4">
-        <v>1414.6</v>
+        <v>1818.3</v>
       </c>
       <c r="V4">
-        <v>0.1529346897737224</v>
+        <v>0.1564344339866132</v>
       </c>
       <c r="W4">
-        <v>0.1373704750370071</v>
+        <v>0.1522860828436291</v>
       </c>
       <c r="X4">
-        <v>0.05271887344160027</v>
+        <v>0.0584674309624672</v>
       </c>
       <c r="Y4">
-        <v>0.08465160159540687</v>
+        <v>0.09381865188116187</v>
       </c>
       <c r="Z4">
-        <v>0.2758366186027254</v>
+        <v>0.2920114287601777</v>
       </c>
       <c r="AA4">
-        <v>0.09715929830533447</v>
+        <v>0.1109192179895247</v>
       </c>
       <c r="AB4">
-        <v>0.04905266530744195</v>
+        <v>0.05465755523875823</v>
       </c>
       <c r="AC4">
-        <v>0.04810663299789252</v>
+        <v>0.05626166275076645</v>
       </c>
       <c r="AD4">
-        <v>3283.3</v>
+        <v>3457.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3283.3</v>
+        <v>3457.3</v>
       </c>
       <c r="AG4">
-        <v>1868.7</v>
+        <v>1639</v>
       </c>
       <c r="AH4">
-        <v>0.2619723928827895</v>
+        <v>0.2292532839987534</v>
       </c>
       <c r="AI4">
-        <v>0.4313321071991593</v>
+        <v>0.4217505336992986</v>
       </c>
       <c r="AJ4">
-        <v>0.1680727442797525</v>
+        <v>0.1235824586801786</v>
       </c>
       <c r="AK4">
-        <v>0.3015296737341466</v>
+        <v>0.2569287684976173</v>
       </c>
       <c r="AL4">
-        <v>33.7</v>
+        <v>40</v>
       </c>
       <c r="AM4">
-        <v>16.1</v>
+        <v>-10</v>
       </c>
       <c r="AN4">
-        <v>4.078126940752702</v>
+        <v>3.641179568193786</v>
       </c>
       <c r="AO4">
-        <v>21.15727002967359</v>
+        <v>22.4225</v>
       </c>
       <c r="AP4">
-        <v>2.321078126940753</v>
+        <v>1.726171669299632</v>
       </c>
       <c r="AQ4">
-        <v>44.28571428571428</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ASA International Group PLC (LSE:ASAI)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.06179999999999999</v>
-      </c>
-      <c r="E5">
-        <v>-0.189</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>8.65</v>
-      </c>
-      <c r="L5">
-        <v>0.0609584214235377</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>66.8</v>
-      </c>
-      <c r="V5">
-        <v>0.8564102564102564</v>
-      </c>
-      <c r="W5">
-        <v>0.08589870903674281</v>
-      </c>
-      <c r="X5">
-        <v>0.07636404514803898</v>
-      </c>
-      <c r="Y5">
-        <v>0.009534663888703832</v>
-      </c>
-      <c r="Z5">
-        <v>0.4445488721804511</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.04682922298384256</v>
-      </c>
-      <c r="AC5">
-        <v>-0.04682922298384256</v>
-      </c>
-      <c r="AD5">
-        <v>253.3</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>253.3</v>
-      </c>
-      <c r="AG5">
-        <v>186.5</v>
-      </c>
-      <c r="AH5">
-        <v>0.7645638394204648</v>
-      </c>
-      <c r="AI5">
-        <v>0.7854263565891473</v>
-      </c>
-      <c r="AJ5">
-        <v>0.7051039697542533</v>
-      </c>
-      <c r="AK5">
-        <v>0.7293703558858037</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
+        <v>-89.69</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_financial_svcs_non_bank_insurance.xlsx
@@ -588,118 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2695</v>
+        <v>0.12075</v>
       </c>
       <c r="E2">
-        <v>0.2855</v>
+        <v>0.05625000000000001</v>
       </c>
       <c r="F2">
-        <v>0.1732</v>
+        <v>0.1892</v>
       </c>
       <c r="G2">
-        <v>0.4720156397465282</v>
+        <v>0.488287728026534</v>
       </c>
       <c r="H2">
-        <v>0.4521504651476338</v>
+        <v>0.4520626036484245</v>
       </c>
       <c r="I2">
-        <v>0.4676014561143319</v>
+        <v>0.46481135986733</v>
       </c>
       <c r="J2">
-        <v>0.3488216757487996</v>
+        <v>0.290229781562182</v>
       </c>
       <c r="K2">
-        <v>1522.3</v>
+        <v>656.7</v>
       </c>
       <c r="L2">
-        <v>0.4104894162060132</v>
+        <v>0.3403296019900498</v>
       </c>
       <c r="M2">
-        <v>456.3</v>
+        <v>459.3</v>
       </c>
       <c r="N2">
-        <v>0.007806124805616714</v>
+        <v>0.03915767935547124</v>
       </c>
       <c r="O2">
-        <v>0.2997438087105038</v>
+        <v>0.6994061215166741</v>
       </c>
       <c r="P2">
-        <v>286.9</v>
+        <v>289.9</v>
       </c>
       <c r="Q2">
-        <v>0.004908124494261309</v>
+        <v>0.02471546101709365</v>
       </c>
       <c r="R2">
-        <v>0.1884648229652499</v>
+        <v>0.4414496726054514</v>
       </c>
       <c r="S2">
         <v>169.4</v>
       </c>
       <c r="T2">
-        <v>0.371246986631602</v>
+        <v>0.3688221206183322</v>
       </c>
       <c r="U2">
-        <v>11177.9</v>
+        <v>1913.6</v>
       </c>
       <c r="V2">
-        <v>0.1912252519498205</v>
+        <v>0.1631442090455689</v>
       </c>
       <c r="W2">
-        <v>0.2243606774443286</v>
+        <v>0.2125066777854509</v>
       </c>
       <c r="X2">
-        <v>0.05734270109563393</v>
+        <v>0.06808485378854087</v>
       </c>
       <c r="Y2">
-        <v>0.1670179763486946</v>
+        <v>0.14442182399691</v>
       </c>
       <c r="Z2">
-        <v>0.6124791491188954</v>
+        <v>0.3057131087803796</v>
+      </c>
+      <c r="AA2">
+        <v>0.05545960899476234</v>
       </c>
       <c r="AB2">
-        <v>0.05539773458889831</v>
+        <v>0.05335229855415263</v>
+      </c>
+      <c r="AC2">
+        <v>0.002107310440609706</v>
       </c>
       <c r="AD2">
-        <v>3705.5</v>
+        <v>3754.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3705.5</v>
+        <v>3754.3</v>
       </c>
       <c r="AG2">
-        <v>-7472.4</v>
+        <v>1840.7</v>
       </c>
       <c r="AH2">
-        <v>0.05961267447023469</v>
+        <v>0.2424663196372984</v>
       </c>
       <c r="AI2">
-        <v>0.3018245499714914</v>
+        <v>0.4377886095433556</v>
       </c>
       <c r="AJ2">
-        <v>-0.1465702399096146</v>
+        <v>0.1356428055592401</v>
       </c>
       <c r="AK2">
-        <v>-6.798653443726683</v>
+        <v>0.2762984088862204</v>
       </c>
       <c r="AL2">
-        <v>57.5</v>
+        <v>40</v>
       </c>
       <c r="AM2">
-        <v>-345.9</v>
+        <v>-10</v>
       </c>
       <c r="AN2">
-        <v>2.014296586214395</v>
+        <v>3.953975776724592</v>
       </c>
       <c r="AO2">
-        <v>30.15826086956521</v>
+        <v>22.4225</v>
       </c>
       <c r="AP2">
-        <v>-4.061969993476843</v>
+        <v>1.938599262769879</v>
       </c>
       <c r="AQ2">
-        <v>-5.013298641225788</v>
+        <v>-89.69</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adyen N.V. (ENXTAM:ADYEN)</t>
+          <t>Euronext N.V. (ENXTPA:ENX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,112 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.344</v>
+        <v>0.195</v>
       </c>
       <c r="E3">
-        <v>0.363</v>
+        <v>0.208</v>
       </c>
       <c r="F3">
-        <v>0.268</v>
+        <v>0.0784</v>
       </c>
       <c r="G3">
-        <v>0.4165481344052772</v>
+        <v>0.5328884112889543</v>
       </c>
       <c r="H3">
-        <v>0.4146052360338074</v>
+        <v>0.4933544482778123</v>
       </c>
       <c r="I3">
-        <v>0.4314574314574315</v>
+        <v>0.5072676884791585</v>
       </c>
       <c r="J3">
-        <v>0.3206396231761593</v>
+        <v>0.3798454685847933</v>
       </c>
       <c r="K3">
-        <v>884.8</v>
+        <v>637.5</v>
       </c>
       <c r="L3">
-        <v>0.4559884559884559</v>
+        <v>0.3605565296080538</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>456.3</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03925701601940912</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.7157647058823529</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>286.9</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02468296711805496</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.4500392156862745</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>169.4</v>
+      </c>
+      <c r="T3">
+        <v>0.371246986631602</v>
       </c>
       <c r="U3">
-        <v>9359.6</v>
+        <v>1818.3</v>
       </c>
       <c r="V3">
-        <v>0.1998603480195684</v>
+        <v>0.1564344339866132</v>
       </c>
       <c r="W3">
-        <v>0.2964352720450281</v>
+        <v>0.1522860828436291</v>
       </c>
       <c r="X3">
-        <v>0.05621797122880066</v>
+        <v>0.05845928693062635</v>
       </c>
       <c r="Y3">
-        <v>0.2402173008162275</v>
+        <v>0.09382679591300272</v>
+      </c>
+      <c r="Z3">
+        <v>0.2920114287601777</v>
+      </c>
+      <c r="AA3">
+        <v>0.1109192179895247</v>
       </c>
       <c r="AB3">
-        <v>0.05613791393903839</v>
+        <v>0.05465127825296189</v>
+      </c>
+      <c r="AC3">
+        <v>0.0562679397365628</v>
       </c>
       <c r="AD3">
-        <v>248.2</v>
+        <v>3457.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>248.2</v>
+        <v>3457.3</v>
       </c>
       <c r="AG3">
-        <v>-9111.4</v>
+        <v>1639</v>
       </c>
       <c r="AH3">
-        <v>0.005272000832644773</v>
+        <v>0.2292532839987534</v>
       </c>
       <c r="AI3">
-        <v>0.06084078931241573</v>
+        <v>0.4217505336992986</v>
       </c>
       <c r="AJ3">
-        <v>-0.2415580352763705</v>
+        <v>0.1235824586801786</v>
       </c>
       <c r="AK3">
-        <v>1.72561125736255</v>
+        <v>0.2569287684976173</v>
       </c>
       <c r="AL3">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="AM3">
-        <v>-335.9</v>
+        <v>-10</v>
       </c>
       <c r="AN3">
-        <v>0.2788450735872374</v>
+        <v>3.641179568193786</v>
       </c>
       <c r="AO3">
-        <v>47.84</v>
+        <v>22.4225</v>
       </c>
       <c r="AP3">
-        <v>-10.23637793506347</v>
+        <v>1.726171669299632</v>
       </c>
       <c r="AQ3">
-        <v>-2.492408454897291</v>
+        <v>-89.69</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Euronext N.V. (ENXTPA:ENX)</t>
+          <t>ASA International Group PLC (LSE:ASAI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,124 +862,112 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.195</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="E4">
-        <v>0.208</v>
+        <v>-0.0955</v>
       </c>
       <c r="F4">
-        <v>0.0784</v>
+        <v>0.3</v>
       </c>
       <c r="G4">
-        <v>0.5328884112889543</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.4933544482778123</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.5072676884791585</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.3798454685847933</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>637.5</v>
+        <v>19.2</v>
       </c>
       <c r="L4">
-        <v>0.3605565296080538</v>
+        <v>0.1188854489164087</v>
       </c>
       <c r="M4">
-        <v>456.3</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>0.03925701601940912</v>
+        <v>0.02827521206409048</v>
       </c>
       <c r="O4">
-        <v>0.7157647058823529</v>
+        <v>0.15625</v>
       </c>
       <c r="P4">
-        <v>286.9</v>
+        <v>3</v>
       </c>
       <c r="Q4">
-        <v>0.02468296711805496</v>
+        <v>0.02827521206409048</v>
       </c>
       <c r="R4">
-        <v>0.4500392156862745</v>
+        <v>0.15625</v>
       </c>
       <c r="S4">
-        <v>169.4</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.371246986631602</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1818.3</v>
+        <v>95.3</v>
       </c>
       <c r="V4">
-        <v>0.1564344339866132</v>
+        <v>0.8982092365692743</v>
       </c>
       <c r="W4">
-        <v>0.1522860828436291</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="X4">
-        <v>0.0584674309624672</v>
+        <v>0.07771042064645541</v>
       </c>
       <c r="Y4">
-        <v>0.09381865188116187</v>
+        <v>0.1950168520808173</v>
       </c>
       <c r="Z4">
-        <v>0.2920114287601777</v>
+        <v>0.6286492798754378</v>
       </c>
       <c r="AA4">
-        <v>0.1109192179895247</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05465755523875823</v>
+        <v>0.05205331885534339</v>
       </c>
       <c r="AC4">
-        <v>0.05626166275076645</v>
+        <v>-0.05205331885534339</v>
       </c>
       <c r="AD4">
-        <v>3457.3</v>
+        <v>297</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3457.3</v>
+        <v>297</v>
       </c>
       <c r="AG4">
-        <v>1639</v>
+        <v>201.7</v>
       </c>
       <c r="AH4">
-        <v>0.2292532839987534</v>
+        <v>0.7367898784420739</v>
       </c>
       <c r="AI4">
-        <v>0.4217505336992986</v>
+        <v>0.7855064797672573</v>
       </c>
       <c r="AJ4">
-        <v>0.1235824586801786</v>
+        <v>0.6552956465237167</v>
       </c>
       <c r="AK4">
-        <v>0.2569287684976173</v>
+        <v>0.7132248939179633</v>
       </c>
       <c r="AL4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-10</v>
-      </c>
-      <c r="AN4">
-        <v>3.641179568193786</v>
-      </c>
-      <c r="AO4">
-        <v>22.4225</v>
-      </c>
-      <c r="AP4">
-        <v>1.726171669299632</v>
-      </c>
-      <c r="AQ4">
-        <v>-89.69</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
